--- a/supplies/116057614-1.xlsx
+++ b/supplies/116057614-1.xlsx
@@ -481,7 +481,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Готова к отгрузке</t>
+          <t>В пути</t>
         </is>
       </c>
     </row>
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-04</t>
         </is>
       </c>
     </row>
@@ -1141,25 +1141,25 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>1022087316635000</t>
+          <t>1022087316702000</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>для кошек и собак 140</t>
+          <t>для кошек и собак 260 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Витамины пивные дрожжи для собак и кошек 8in1 EXCEL Brewer's Yeast 140 шт</t>
+          <t>Витамины пивные дрожжи для собак и кошек 8in1 EXCEL Brewer's Yeast 260 шт</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ростов</t>
+          <t>Казань</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1168,7 +1168,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>2000057635037</v>
+        <v>2000057635038</v>
       </c>
     </row>
     <row r="17">
@@ -1177,25 +1177,25 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>1022087316635000</t>
+          <t>1022087316702000</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>кальций</t>
+          <t>для кошек и собак 140</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Витамины для щенков и собак кальций calcium 155 таблеток</t>
+          <t>Витамины пивные дрожжи для собак и кошек 8in1 EXCEL Brewer's Yeast 140 шт</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ростов</t>
+          <t>Казань</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1204,7 +1204,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>2000057635037</v>
+        <v>2000057635038</v>
       </c>
     </row>
     <row r="18">
@@ -1213,25 +1213,25 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>1022087316635000</t>
+          <t>1022087316702000</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Multi Vit Puppy</t>
+          <t>кальций</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Витамины для щенков и растущих собак 100 таблеток</t>
+          <t>Витамины для щенков и собак кальций calcium 155 таблеток</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ростов</t>
+          <t>Казань</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>2000057635037</v>
+        <v>2000057635038</v>
       </c>
     </row>
     <row r="19">
@@ -1249,25 +1249,25 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>1022087316635000</t>
+          <t>1022087316702000</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>для мелких пород</t>
+          <t>Multi Vit Puppy</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Витамины для собак мелких пород 70 таблеток</t>
+          <t>Витамины для щенков и растущих собак 100 таблеток</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ростов</t>
+          <t>Казань</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1276,7 +1276,7 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>2000057635037</v>
+        <v>2000057635038</v>
       </c>
     </row>
     <row r="20">
@@ -1285,17 +1285,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>1022087316635000</t>
+          <t>1022087316702000</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>бреверсы для крупных</t>
+          <t>для мелких пород</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Витамины для собак крупных пород 80 таблеток</t>
+          <t>Витамины для собак мелких пород 70 таблеток</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -1303,7 +1303,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ростов</t>
+          <t>Казань</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1312,7 +1312,7 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>2000057635037</v>
+        <v>2000057635038</v>
       </c>
     </row>
     <row r="21">
@@ -1321,25 +1321,25 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>1022087316635000</t>
+          <t>1022087316702000</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>глюкозамин 55 шт</t>
+          <t>бреверсы для крупных</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Витамины для собак Glucosamine для суставов 55 таблеток</t>
+          <t>Витамины для собак крупных пород 80 таблеток</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ростов</t>
+          <t>Казань</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1348,7 +1348,7 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>2000057635037</v>
+        <v>2000057635038</v>
       </c>
     </row>
     <row r="22">
@@ -1357,25 +1357,25 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>1022087316635000</t>
+          <t>1022087316702000</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>для пожилых собак1</t>
+          <t>глюкозамин 55 шт</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Витамины для пожилых собак от 5 лет 70 таблеток</t>
+          <t>Витамины для собак Glucosamine для суставов 55 таблеток</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ростов</t>
+          <t>Казань</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1384,12 +1384,12 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>2000057635037</v>
+        <v>2000057635038</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -1398,16 +1398,16 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>для кошек и собак 260 1</t>
+          <t>для пожилых собак1</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Витамины пивные дрожжи для собак и кошек 8in1 EXCEL Brewer's Yeast 260 шт</t>
+          <t>Витамины для пожилых собак от 5 лет 70 таблеток</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1429,17 +1429,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>1022087316702000</t>
+          <t>1022087316050000</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>для кошек и собак 140</t>
+          <t>для кошек и собак 260 1</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Витамины пивные дрожжи для собак и кошек 8in1 EXCEL Brewer's Yeast 140 шт</t>
+          <t>Витамины пивные дрожжи для собак и кошек 8in1 EXCEL Brewer's Yeast 260 шт</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Казань</t>
+          <t>Санкт-Петербург и СЗО</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1456,7 +1456,7 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>2000057635038</v>
+        <v>2000057635032</v>
       </c>
     </row>
     <row r="25">
@@ -1465,7 +1465,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>1022087316702000</t>
+          <t>1022087316050000</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1479,11 +1479,11 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Казань</t>
+          <t>Санкт-Петербург и СЗО</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1492,7 +1492,7 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>2000057635038</v>
+        <v>2000057635032</v>
       </c>
     </row>
     <row r="26">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>1022087316702000</t>
+          <t>1022087316050000</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1515,11 +1515,11 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Казань</t>
+          <t>Санкт-Петербург и СЗО</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1528,7 +1528,7 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>2000057635038</v>
+        <v>2000057635032</v>
       </c>
     </row>
     <row r="27">
@@ -1537,7 +1537,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>1022087316702000</t>
+          <t>1022087316050000</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1551,11 +1551,11 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Казань</t>
+          <t>Санкт-Петербург и СЗО</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1564,7 +1564,7 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>2000057635038</v>
+        <v>2000057635032</v>
       </c>
     </row>
     <row r="28">
@@ -1573,7 +1573,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>1022087316702000</t>
+          <t>1022087316050000</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1591,7 +1591,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Казань</t>
+          <t>Санкт-Петербург и СЗО</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1600,7 +1600,7 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>2000057635038</v>
+        <v>2000057635032</v>
       </c>
     </row>
     <row r="29">
@@ -1609,7 +1609,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>1022087316702000</t>
+          <t>1022087316050000</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1623,11 +1623,11 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Казань</t>
+          <t>Санкт-Петербург и СЗО</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1636,34 +1636,34 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>2000057635038</v>
+        <v>2000057635032</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>1022087316702000</t>
+          <t>1022087316141000</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>для пожилых собак1</t>
+          <t>для кошек и собак 140</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Витамины для пожилых собак от 5 лет 70 таблеток</t>
+          <t>Витамины пивные дрожжи для собак и кошек 8in1 EXCEL Brewer's Yeast 140 шт</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Казань</t>
+          <t>Санкт-Петербург и СЗО</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -1672,7 +1672,7 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>2000057635038</v>
+        <v>2000057635032</v>
       </c>
     </row>
     <row r="31">
@@ -1681,17 +1681,17 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>1022087316050000</t>
+          <t>1022087316141000</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>для кошек и собак 260 1</t>
+          <t>кальций</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Витамины пивные дрожжи для собак и кошек 8in1 EXCEL Brewer's Yeast 260 шт</t>
+          <t>Витамины для щенков и собак кальций calcium 155 таблеток</t>
         </is>
       </c>
       <c r="E31" t="n">
@@ -1717,21 +1717,21 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>1022087316050000</t>
+          <t>1022087316141000</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>кальций</t>
+          <t>для пожилых собак1</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Витамины для щенков и собак кальций calcium 155 таблеток</t>
+          <t>Витамины для пожилых собак от 5 лет 70 таблеток</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -1749,21 +1749,21 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>1022087316050000</t>
+          <t>1022087316529000</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Multi Vit Puppy</t>
+          <t>для кошек и собак 260 1</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Витамины для щенков и растущих собак 100 таблеток</t>
+          <t>Витамины пивные дрожжи для собак и кошек 8in1 EXCEL Brewer's Yeast 260 шт</t>
         </is>
       </c>
       <c r="E33" t="n">
@@ -1771,7 +1771,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Санкт-Петербург и СЗО</t>
+          <t>Краснодар</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -1780,34 +1780,34 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>2000057635032</v>
+        <v>2000057635035</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
+        <v>7</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>1022087316529000</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>для кошек и собак 140</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Витамины пивные дрожжи для собак и кошек 8in1 EXCEL Brewer's Yeast 140 шт</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
         <v>6</v>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>1022087316050000</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>для мелких пород</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>Витамины для собак мелких пород 70 таблеток</t>
-        </is>
-      </c>
-      <c r="E34" t="n">
-        <v>15</v>
-      </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Санкт-Петербург и СЗО</t>
+          <t>Краснодар</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -1816,34 +1816,34 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>2000057635032</v>
+        <v>2000057635035</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>1022087316050000</t>
+          <t>1022087316529000</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>бреверсы для крупных</t>
+          <t>кальций</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Витамины для собак крупных пород 80 таблеток</t>
+          <t>Витамины для щенков и собак кальций calcium 155 таблеток</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Санкт-Петербург и СЗО</t>
+          <t>Краснодар</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -1852,34 +1852,34 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>2000057635032</v>
+        <v>2000057635035</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>1022087316050000</t>
+          <t>1022087316529000</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>глюкозамин 55 шт</t>
+          <t>для мелких пород</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Витамины для собак Glucosamine для суставов 55 таблеток</t>
+          <t>Витамины для собак мелких пород 70 таблеток</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Санкт-Петербург и СЗО</t>
+          <t>Краснодар</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -1888,7 +1888,7 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>2000057635032</v>
+        <v>2000057635035</v>
       </c>
     </row>
     <row r="37">
@@ -1897,25 +1897,25 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>1022087316141000</t>
+          <t>1022087316529000</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>для кошек и собак 140</t>
+          <t>бреверсы для крупных</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Витамины пивные дрожжи для собак и кошек 8in1 EXCEL Brewer's Yeast 140 шт</t>
+          <t>Витамины для собак крупных пород 80 таблеток</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Санкт-Петербург и СЗО</t>
+          <t>Краснодар</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -1924,7 +1924,7 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>2000057635032</v>
+        <v>2000057635035</v>
       </c>
     </row>
     <row r="38">
@@ -1933,25 +1933,25 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>1022087316141000</t>
+          <t>1022087316529000</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>кальций</t>
+          <t>глюкозамин 55 шт</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Витамины для щенков и собак кальций calcium 155 таблеток</t>
+          <t>Витамины для собак Glucosamine для суставов 55 таблеток</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Санкт-Петербург и СЗО</t>
+          <t>Краснодар</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -1960,7 +1960,7 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>2000057635032</v>
+        <v>2000057635035</v>
       </c>
     </row>
     <row r="39">
@@ -1969,7 +1969,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>1022087316141000</t>
+          <t>1022087316529000</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1983,11 +1983,11 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Санкт-Петербург и СЗО</t>
+          <t>Краснодар</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -1996,7 +1996,7 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>2000057635032</v>
+        <v>2000057635035</v>
       </c>
     </row>
     <row r="40">
@@ -2005,7 +2005,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>1022087316529000</t>
+          <t>1022087358325000</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2019,11 +2019,11 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Краснодар</t>
+          <t>Москва, МО и Дальние регионы</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2032,7 +2032,7 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>2000057635035</v>
+        <v>2000057635039</v>
       </c>
     </row>
     <row r="41">
@@ -2041,25 +2041,25 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>1022087316529000</t>
+          <t>1022087358325000</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>для кошек и собак 140</t>
+          <t>кальций</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Витамины пивные дрожжи для собак и кошек 8in1 EXCEL Brewer's Yeast 140 шт</t>
+          <t>Витамины для щенков и собак кальций calcium 155 таблеток</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6</v>
+        <v>35</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Краснодар</t>
+          <t>Москва, МО и Дальние регионы</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -2068,34 +2068,34 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>2000057635035</v>
+        <v>2000057635039</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>1022087316529000</t>
+          <t>1022087358326000</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>кальций</t>
+          <t>для мелких пород</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Витамины для щенков и собак кальций calcium 155 таблеток</t>
+          <t>Витамины для собак мелких пород 70 таблеток</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Краснодар</t>
+          <t>Москва, МО и Дальние регионы</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -2104,34 +2104,34 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>2000057635035</v>
+        <v>2000057635039</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>1022087316529000</t>
+          <t>1022087358326000</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>для мелких пород</t>
+          <t>бреверсы для крупных</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Витамины для собак мелких пород 70 таблеток</t>
+          <t>Витамины для собак крупных пород 80 таблеток</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Краснодар</t>
+          <t>Москва, МО и Дальние регионы</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2140,34 +2140,34 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>2000057635035</v>
+        <v>2000057635039</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>1022087316529000</t>
+          <t>1022087358327000</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>бреверсы для крупных</t>
+          <t>Multi Vit Puppy</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Витамины для собак крупных пород 80 таблеток</t>
+          <t>Витамины для щенков и растущих собак 100 таблеток</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Краснодар</t>
+          <t>Москва, МО и Дальние регионы</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -2176,16 +2176,16 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>2000057635035</v>
+        <v>2000057635039</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>1022087316529000</t>
+          <t>1022087358327000</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2199,11 +2199,11 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Краснодар</t>
+          <t>Москва, МО и Дальние регионы</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -2212,16 +2212,16 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>2000057635035</v>
+        <v>2000057635039</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>1022087316529000</t>
+          <t>1022087358327000</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2235,11 +2235,11 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Краснодар</t>
+          <t>Москва, МО и Дальние регионы</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -2248,16 +2248,16 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>2000057635035</v>
+        <v>2000057635039</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>1022087316573000</t>
+          <t>1022087358328000</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2271,11 +2271,11 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6</v>
+        <v>70</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Тюмень</t>
+          <t>Москва, МО и Дальние регионы</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -2284,34 +2284,34 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>2000057635036</v>
+        <v>2000057635039</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>1022087316573000</t>
+          <t>1022087316635000</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>кальций</t>
+          <t>для кошек и собак 140</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Витамины для щенков и собак кальций calcium 155 таблеток</t>
+          <t>Витамины пивные дрожжи для собак и кошек 8in1 EXCEL Brewer's Yeast 140 шт</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Тюмень</t>
+          <t>Ростов</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -2320,26 +2320,26 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>2000057635036</v>
+        <v>2000057635037</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>1022087316573000</t>
+          <t>1022087316635000</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>глюкозамин 55 шт</t>
+          <t>кальций</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Витамины для собак Glucosamine для суставов 55 таблеток</t>
+          <t>Витамины для щенков и собак кальций calcium 155 таблеток</t>
         </is>
       </c>
       <c r="E49" t="n">
@@ -2347,7 +2347,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Тюмень</t>
+          <t>Ростов</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -2356,34 +2356,34 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>2000057635036</v>
+        <v>2000057635037</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>1022087358325000</t>
+          <t>1022087316635000</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>для кошек и собак 260 1</t>
+          <t>Multi Vit Puppy</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Витамины пивные дрожжи для собак и кошек 8in1 EXCEL Brewer's Yeast 260 шт</t>
+          <t>Витамины для щенков и растущих собак 100 таблеток</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Москва, МО и Дальние регионы</t>
+          <t>Ростов</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -2392,34 +2392,34 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>2000057635039</v>
+        <v>2000057635037</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>1022087358325000</t>
+          <t>1022087316635000</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>кальций</t>
+          <t>для мелких пород</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Витамины для щенков и собак кальций calcium 155 таблеток</t>
+          <t>Витамины для собак мелких пород 70 таблеток</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Москва, МО и Дальние регионы</t>
+          <t>Ростов</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -2428,34 +2428,34 @@
         </is>
       </c>
       <c r="H51" t="n">
-        <v>2000057635039</v>
+        <v>2000057635037</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>1022087358326000</t>
+          <t>1022087316635000</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>для мелких пород</t>
+          <t>бреверсы для крупных</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Витамины для собак мелких пород 70 таблеток</t>
+          <t>Витамины для собак крупных пород 80 таблеток</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Москва, МО и Дальние регионы</t>
+          <t>Ростов</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -2464,34 +2464,34 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>2000057635039</v>
+        <v>2000057635037</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>1022087358326000</t>
+          <t>1022087316635000</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>бреверсы для крупных</t>
+          <t>глюкозамин 55 шт</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Витамины для собак крупных пород 80 таблеток</t>
+          <t>Витамины для собак Glucosamine для суставов 55 таблеток</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Москва, МО и Дальние регионы</t>
+          <t>Ростов</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -2500,7 +2500,7 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>2000057635039</v>
+        <v>2000057635037</v>
       </c>
     </row>
     <row r="54">
@@ -2509,25 +2509,25 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>1022087358327000</t>
+          <t>1022087316635000</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Multi Vit Puppy</t>
+          <t>для пожилых собак1</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Витамины для щенков и растущих собак 100 таблеток</t>
+          <t>Витамины для пожилых собак от 5 лет 70 таблеток</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Москва, МО и Дальние регионы</t>
+          <t>Ростов</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -2536,34 +2536,34 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>2000057635039</v>
+        <v>2000057635037</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>1022087358327000</t>
+          <t>1022087358727000</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>глюкозамин 55 шт</t>
+          <t>для кошек и собак 260 1</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Витамины для собак Glucosamine для суставов 55 таблеток</t>
+          <t>Витамины пивные дрожжи для собак и кошек 8in1 EXCEL Brewer's Yeast 260 шт</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Москва, МО и Дальние регионы</t>
+          <t>Екатеринбург</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -2572,34 +2572,34 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>2000057635039</v>
+        <v>2000057635042</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>1022087358327000</t>
+          <t>1022087358727000</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>для пожилых собак1</t>
+          <t>для кошек и собак 140</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Витамины для пожилых собак от 5 лет 70 таблеток</t>
+          <t>Витамины пивные дрожжи для собак и кошек 8in1 EXCEL Brewer's Yeast 140 шт</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Москва, МО и Дальние регионы</t>
+          <t>Екатеринбург</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -2608,7 +2608,7 @@
         </is>
       </c>
       <c r="H56" t="n">
-        <v>2000057635039</v>
+        <v>2000057635042</v>
       </c>
     </row>
     <row r="57">
@@ -2617,25 +2617,25 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>1022087358328000</t>
+          <t>1022087358727000</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>для кошек и собак 140</t>
+          <t>кальций</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Витамины пивные дрожжи для собак и кошек 8in1 EXCEL Brewer's Yeast 140 шт</t>
+          <t>Витамины для щенков и собак кальций calcium 155 таблеток</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>70</v>
+        <v>7</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Москва, МО и Дальние регионы</t>
+          <t>Екатеринбург</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -2644,34 +2644,34 @@
         </is>
       </c>
       <c r="H57" t="n">
-        <v>2000057635039</v>
+        <v>2000057635042</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>1022087358589000</t>
+          <t>1022087358727000</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>для кошек и собак 140</t>
+          <t>глюкозамин 55 шт</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Витамины пивные дрожжи для собак и кошек 8in1 EXCEL Brewer's Yeast 140 шт</t>
+          <t>Витамины для собак Glucosamine для суставов 55 таблеток</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ярославль</t>
+          <t>Екатеринбург</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -2680,34 +2680,34 @@
         </is>
       </c>
       <c r="H58" t="n">
-        <v>2000057635040</v>
+        <v>2000057635042</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>1022087358589000</t>
+          <t>1022087358727000</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>кальций</t>
+          <t>для пожилых собак1</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Витамины для щенков и собак кальций calcium 155 таблеток</t>
+          <t>Витамины для пожилых собак от 5 лет 70 таблеток</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Ярославль</t>
+          <t>Екатеринбург</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -2716,7 +2716,7 @@
         </is>
       </c>
       <c r="H59" t="n">
-        <v>2000057635040</v>
+        <v>2000057635042</v>
       </c>
     </row>
     <row r="60">
@@ -2725,25 +2725,25 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>1022087358589000</t>
+          <t>1022087316573000</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>бреверсы для крупных</t>
+          <t>для кошек и собак 140</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Витамины для собак крупных пород 80 таблеток</t>
+          <t>Витамины пивные дрожжи для собак и кошек 8in1 EXCEL Brewer's Yeast 140 шт</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Ярославль</t>
+          <t>Тюмень</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -2752,7 +2752,7 @@
         </is>
       </c>
       <c r="H60" t="n">
-        <v>2000057635040</v>
+        <v>2000057635036</v>
       </c>
     </row>
     <row r="61">
@@ -2761,25 +2761,25 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>1022087358589000</t>
+          <t>1022087316573000</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>глюкозамин 55 шт</t>
+          <t>кальций</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Витамины для собак Glucosamine для суставов 55 таблеток</t>
+          <t>Витамины для щенков и собак кальций calcium 155 таблеток</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ярославль</t>
+          <t>Тюмень</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -2788,7 +2788,7 @@
         </is>
       </c>
       <c r="H61" t="n">
-        <v>2000057635040</v>
+        <v>2000057635036</v>
       </c>
     </row>
     <row r="62">
@@ -2797,25 +2797,25 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>1022087358589000</t>
+          <t>1022087316573000</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>для пожилых собак1</t>
+          <t>глюкозамин 55 шт</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Витамины для пожилых собак от 5 лет 70 таблеток</t>
+          <t>Витамины для собак Glucosamine для суставов 55 таблеток</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Ярославль</t>
+          <t>Тюмень</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -2824,7 +2824,7 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>2000057635040</v>
+        <v>2000057635036</v>
       </c>
     </row>
     <row r="63">
@@ -2977,25 +2977,25 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>1022087358727000</t>
+          <t>1022087358589000</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>для кошек и собак 260 1</t>
+          <t>для кошек и собак 140</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Витамины пивные дрожжи для собак и кошек 8in1 EXCEL Brewer's Yeast 260 шт</t>
+          <t>Витамины пивные дрожжи для собак и кошек 8in1 EXCEL Brewer's Yeast 140 шт</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Екатеринбург</t>
+          <t>Ярославль</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -3004,7 +3004,7 @@
         </is>
       </c>
       <c r="H67" t="n">
-        <v>2000057635042</v>
+        <v>2000057635040</v>
       </c>
     </row>
     <row r="68">
@@ -3013,17 +3013,17 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>1022087358727000</t>
+          <t>1022087358589000</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>для кошек и собак 140</t>
+          <t>кальций</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Витамины пивные дрожжи для собак и кошек 8in1 EXCEL Brewer's Yeast 140 шт</t>
+          <t>Витамины для щенков и собак кальций calcium 155 таблеток</t>
         </is>
       </c>
       <c r="E68" t="n">
@@ -3031,7 +3031,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Екатеринбург</t>
+          <t>Ярославль</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -3040,7 +3040,7 @@
         </is>
       </c>
       <c r="H68" t="n">
-        <v>2000057635042</v>
+        <v>2000057635040</v>
       </c>
     </row>
     <row r="69">
@@ -3049,25 +3049,25 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>1022087358727000</t>
+          <t>1022087358589000</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>кальций</t>
+          <t>бреверсы для крупных</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Витамины для щенков и собак кальций calcium 155 таблеток</t>
+          <t>Витамины для собак крупных пород 80 таблеток</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Екатеринбург</t>
+          <t>Ярославль</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -3076,7 +3076,7 @@
         </is>
       </c>
       <c r="H69" t="n">
-        <v>2000057635042</v>
+        <v>2000057635040</v>
       </c>
     </row>
     <row r="70">
@@ -3085,7 +3085,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>1022087358727000</t>
+          <t>1022087358589000</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -3099,11 +3099,11 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Екатеринбург</t>
+          <t>Ярославль</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -3112,7 +3112,7 @@
         </is>
       </c>
       <c r="H70" t="n">
-        <v>2000057635042</v>
+        <v>2000057635040</v>
       </c>
     </row>
     <row r="71">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>1022087358727000</t>
+          <t>1022087358589000</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -3135,11 +3135,11 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Екатеринбург</t>
+          <t>Ярославль</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -3148,7 +3148,7 @@
         </is>
       </c>
       <c r="H71" t="n">
-        <v>2000057635042</v>
+        <v>2000057635040</v>
       </c>
     </row>
   </sheetData>
@@ -3245,19 +3245,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D3" t="n">
         <v>4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1022087316635000</t>
+          <t>1022087316702000</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ростов</t>
+          <t>Казань</t>
         </is>
       </c>
     </row>
@@ -3273,19 +3273,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D4" t="n">
         <v>5</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1022087316702000</t>
+          <t>1022087316050000</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Казань</t>
+          <t>Санкт-Петербург и СЗО</t>
         </is>
       </c>
     </row>
@@ -3301,19 +3301,19 @@
         </is>
       </c>
       <c r="C5" t="n">
+        <v>15</v>
+      </c>
+      <c r="D5" t="n">
         <v>10</v>
       </c>
-      <c r="D5" t="n">
-        <v>6</v>
-      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1022087316050000</t>
+          <t>1022087358327000</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Санкт-Петербург и СЗО</t>
+          <t>Москва, МО и Дальние регионы</t>
         </is>
       </c>
     </row>
@@ -3329,19 +3329,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D6" t="n">
         <v>12</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1022087358327000</t>
+          <t>1022087316635000</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Москва, МО и Дальние регионы</t>
+          <t>Ростов</t>
         </is>
       </c>
     </row>
@@ -3420,12 +3420,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1022087316635000</t>
+          <t>1022087316702000</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ростов</t>
+          <t>Казань</t>
         </is>
       </c>
     </row>
@@ -3448,12 +3448,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1022087316702000</t>
+          <t>1022087316050000</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Казань</t>
+          <t>Санкт-Петербург и СЗО</t>
         </is>
       </c>
     </row>
@@ -3472,16 +3472,16 @@
         <v>10</v>
       </c>
       <c r="D11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1022087316050000</t>
+          <t>1022087316529000</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Санкт-Петербург и СЗО</t>
+          <t>Краснодар</t>
         </is>
       </c>
     </row>
@@ -3497,19 +3497,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1022087316529000</t>
+          <t>1022087358326000</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Краснодар</t>
+          <t>Москва, МО и Дальние регионы</t>
         </is>
       </c>
     </row>
@@ -3525,19 +3525,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1022087358326000</t>
+          <t>1022087316635000</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Москва, МО и Дальние регионы</t>
+          <t>Ростов</t>
         </is>
       </c>
     </row>
@@ -3556,7 +3556,7 @@
         <v>5</v>
       </c>
       <c r="D14" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -3672,12 +3672,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1022087316635000</t>
+          <t>1022087316702000</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ростов</t>
+          <t>Казань</t>
         </is>
       </c>
     </row>
@@ -3693,19 +3693,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="D19" t="n">
         <v>5</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1022087316702000</t>
+          <t>1022087316050000</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Казань</t>
+          <t>Санкт-Петербург и СЗО</t>
         </is>
       </c>
     </row>
@@ -3721,19 +3721,19 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D20" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1022087316050000</t>
+          <t>1022087316529000</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Санкт-Петербург и СЗО</t>
+          <t>Краснодар</t>
         </is>
       </c>
     </row>
@@ -3749,19 +3749,19 @@
         </is>
       </c>
       <c r="C21" t="n">
+        <v>25</v>
+      </c>
+      <c r="D21" t="n">
         <v>10</v>
       </c>
-      <c r="D21" t="n">
-        <v>8</v>
-      </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1022087316529000</t>
+          <t>1022087358327000</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Краснодар</t>
+          <t>Москва, МО и Дальние регионы</t>
         </is>
       </c>
     </row>
@@ -3777,19 +3777,19 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D22" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1022087316573000</t>
+          <t>1022087316635000</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Тюмень</t>
+          <t>Ростов</t>
         </is>
       </c>
     </row>
@@ -3805,19 +3805,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="D23" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1022087358327000</t>
+          <t>1022087358727000</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Москва, МО и Дальние регионы</t>
+          <t>Екатеринбург</t>
         </is>
       </c>
     </row>
@@ -3833,19 +3833,19 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D24" t="n">
         <v>14</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1022087358589000</t>
+          <t>1022087316573000</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ярославль</t>
+          <t>Тюмень</t>
         </is>
       </c>
     </row>
@@ -3889,19 +3889,19 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D26" t="n">
         <v>16</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1022087358727000</t>
+          <t>1022087358589000</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Екатеринбург</t>
+          <t>Ярославль</t>
         </is>
       </c>
     </row>
@@ -4008,12 +4008,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1022087316635000</t>
+          <t>1022087316702000</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ростов</t>
+          <t>Казань</t>
         </is>
       </c>
     </row>
@@ -4029,19 +4029,19 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="D31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1022087316702000</t>
+          <t>1022087316141000</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Казань</t>
+          <t>Санкт-Петербург и СЗО</t>
         </is>
       </c>
     </row>
@@ -4057,19 +4057,19 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>35</v>
+        <v>6</v>
       </c>
       <c r="D32" t="n">
         <v>7</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1022087316141000</t>
+          <t>1022087316529000</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Санкт-Петербург и СЗО</t>
+          <t>Краснодар</t>
         </is>
       </c>
     </row>
@@ -4085,19 +4085,19 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>6</v>
+        <v>70</v>
       </c>
       <c r="D33" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1022087316529000</t>
+          <t>1022087358328000</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Краснодар</t>
+          <t>Москва, МО и Дальние регионы</t>
         </is>
       </c>
     </row>
@@ -4113,19 +4113,19 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="D34" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1022087316573000</t>
+          <t>1022087316635000</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Тюмень</t>
+          <t>Ростов</t>
         </is>
       </c>
     </row>
@@ -4141,19 +4141,19 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>70</v>
+        <v>10</v>
       </c>
       <c r="D35" t="n">
         <v>13</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1022087358328000</t>
+          <t>1022087358727000</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Москва, МО и Дальние регионы</t>
+          <t>Екатеринбург</t>
         </is>
       </c>
     </row>
@@ -4169,19 +4169,19 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="D36" t="n">
         <v>14</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1022087358589000</t>
+          <t>1022087316573000</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ярославль</t>
+          <t>Тюмень</t>
         </is>
       </c>
     </row>
@@ -4225,19 +4225,19 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D38" t="n">
         <v>16</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>1022087358727000</t>
+          <t>1022087358589000</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Екатеринбург</t>
+          <t>Ярославль</t>
         </is>
       </c>
     </row>
@@ -4284,7 +4284,7 @@
         <v>8</v>
       </c>
       <c r="D40" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -4312,7 +4312,7 @@
         <v>15</v>
       </c>
       <c r="D41" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -4340,7 +4340,7 @@
         <v>10</v>
       </c>
       <c r="D42" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -4368,7 +4368,7 @@
         <v>25</v>
       </c>
       <c r="D43" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -4396,7 +4396,7 @@
         <v>5</v>
       </c>
       <c r="D44" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -4449,19 +4449,19 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D46" t="n">
         <v>4</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>1022087316635000</t>
+          <t>1022087316702000</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ростов</t>
+          <t>Казань</t>
         </is>
       </c>
     </row>
@@ -4477,19 +4477,19 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D47" t="n">
         <v>5</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>1022087316702000</t>
+          <t>1022087316050000</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Казань</t>
+          <t>Санкт-Петербург и СЗО</t>
         </is>
       </c>
     </row>
@@ -4505,19 +4505,19 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D48" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>1022087316050000</t>
+          <t>1022087316529000</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Санкт-Петербург и СЗО</t>
+          <t>Краснодар</t>
         </is>
       </c>
     </row>
@@ -4533,19 +4533,19 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="D49" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>1022087316529000</t>
+          <t>1022087358326000</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Краснодар</t>
+          <t>Москва, МО и Дальние регионы</t>
         </is>
       </c>
     </row>
@@ -4561,19 +4561,19 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="D50" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>1022087358326000</t>
+          <t>1022087316635000</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Москва, МО и Дальние регионы</t>
+          <t>Ростов</t>
         </is>
       </c>
     </row>
@@ -4617,19 +4617,19 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D52" t="n">
         <v>4</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>1022087316635000</t>
+          <t>1022087316702000</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ростов</t>
+          <t>Казань</t>
         </is>
       </c>
     </row>
@@ -4645,19 +4645,19 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D53" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>1022087316702000</t>
+          <t>1022087316141000</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Казань</t>
+          <t>Санкт-Петербург и СЗО</t>
         </is>
       </c>
     </row>
@@ -4673,19 +4673,19 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="D54" t="n">
         <v>7</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>1022087316141000</t>
+          <t>1022087316529000</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Санкт-Петербург и СЗО</t>
+          <t>Краснодар</t>
         </is>
       </c>
     </row>
@@ -4701,19 +4701,19 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="D55" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>1022087316529000</t>
+          <t>1022087358327000</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Краснодар</t>
+          <t>Москва, МО и Дальние регионы</t>
         </is>
       </c>
     </row>
@@ -4729,19 +4729,19 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="D56" t="n">
         <v>12</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>1022087358327000</t>
+          <t>1022087316635000</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Москва, МО и Дальние регионы</t>
+          <t>Ростов</t>
         </is>
       </c>
     </row>
@@ -4757,19 +4757,19 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D57" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>1022087358589000</t>
+          <t>1022087358727000</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ярославль</t>
+          <t>Екатеринбург</t>
         </is>
       </c>
     </row>
@@ -4785,19 +4785,19 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D58" t="n">
         <v>16</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>1022087358727000</t>
+          <t>1022087358589000</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Екатеринбург</t>
+          <t>Ярославль</t>
         </is>
       </c>
     </row>
@@ -4897,19 +4897,19 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D62" t="n">
         <v>4</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>1022087316635000</t>
+          <t>1022087316702000</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Ростов</t>
+          <t>Казань</t>
         </is>
       </c>
     </row>
@@ -4925,19 +4925,19 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D63" t="n">
         <v>5</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>1022087316702000</t>
+          <t>1022087316050000</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Казань</t>
+          <t>Санкт-Петербург и СЗО</t>
         </is>
       </c>
     </row>
@@ -4953,14 +4953,14 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="D64" t="n">
         <v>6</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>1022087316050000</t>
+          <t>1022087316141000</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -4981,19 +4981,19 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="D65" t="n">
         <v>7</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>1022087316141000</t>
+          <t>1022087316529000</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Санкт-Петербург и СЗО</t>
+          <t>Краснодар</t>
         </is>
       </c>
     </row>
@@ -5009,19 +5009,19 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>5</v>
+        <v>35</v>
       </c>
       <c r="D66" t="n">
         <v>8</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>1022087316529000</t>
+          <t>1022087358325000</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Краснодар</t>
+          <t>Москва, МО и Дальние регионы</t>
         </is>
       </c>
     </row>
@@ -5040,16 +5040,16 @@
         <v>5</v>
       </c>
       <c r="D67" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>1022087316573000</t>
+          <t>1022087316635000</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Тюмень</t>
+          <t>Ростов</t>
         </is>
       </c>
     </row>
@@ -5065,19 +5065,19 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="D68" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>1022087358325000</t>
+          <t>1022087358727000</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Москва, МО и Дальние регионы</t>
+          <t>Екатеринбург</t>
         </is>
       </c>
     </row>
@@ -5093,19 +5093,19 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D69" t="n">
         <v>14</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>1022087358589000</t>
+          <t>1022087316573000</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Ярославль</t>
+          <t>Тюмень</t>
         </is>
       </c>
     </row>
@@ -5149,19 +5149,19 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D71" t="n">
         <v>16</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>1022087358727000</t>
+          <t>1022087358589000</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Екатеринбург</t>
+          <t>Ярославль</t>
         </is>
       </c>
     </row>

--- a/supplies/116057614-1.xlsx
+++ b/supplies/116057614-1.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Инфо" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ПО КОРОБАМ" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ПО ТОВАРУ" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Инфо" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ПО КОРОБАМ" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="ПО ТОВАРУ" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/supplies/116057614-1.xlsx
+++ b/supplies/116057614-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
     </row>

--- a/supplies/116057614-1.xlsx
+++ b/supplies/116057614-1.xlsx
@@ -481,7 +481,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>В пути</t>
+          <t>ACCEPTANCE_AT_STORAGE_WAREHOUSE</t>
         </is>
       </c>
     </row>

--- a/supplies/116057614-1.xlsx
+++ b/supplies/116057614-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
     </row>

--- a/supplies/116057614-1.xlsx
+++ b/supplies/116057614-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
     </row>

--- a/supplies/116057614-1.xlsx
+++ b/supplies/116057614-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>

--- a/supplies/116057614-1.xlsx
+++ b/supplies/116057614-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
     </row>

--- a/supplies/116057614-1.xlsx
+++ b/supplies/116057614-1.xlsx
@@ -481,7 +481,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>В пути</t>
+          <t>ACCEPTANCE_AT_STORAGE_WAREHOUSE</t>
         </is>
       </c>
     </row>
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
     </row>

--- a/supplies/116057614-1.xlsx
+++ b/supplies/116057614-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>

--- a/supplies/116057614-1.xlsx
+++ b/supplies/116057614-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>

--- a/supplies/116057614-1.xlsx
+++ b/supplies/116057614-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>

--- a/supplies/116057614-1.xlsx
+++ b/supplies/116057614-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>

--- a/supplies/116057614-1.xlsx
+++ b/supplies/116057614-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>

--- a/supplies/116057614-1.xlsx
+++ b/supplies/116057614-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
     </row>

--- a/supplies/116057614-1.xlsx
+++ b/supplies/116057614-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
     </row>

--- a/supplies/116057614-1.xlsx
+++ b/supplies/116057614-1.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Инфо" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="ПО КОРОБАМ" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="ПО ТОВАРУ" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Инфо" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ПО КОРОБАМ" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ПО ТОВАРУ" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/supplies/116057614-1.xlsx
+++ b/supplies/116057614-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>

--- a/supplies/116057614-1.xlsx
+++ b/supplies/116057614-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>

--- a/supplies/116057614-1.xlsx
+++ b/supplies/116057614-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>

--- a/supplies/116057614-1.xlsx
+++ b/supplies/116057614-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
     </row>

--- a/supplies/116057614-1.xlsx
+++ b/supplies/116057614-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>

--- a/supplies/116057614-1.xlsx
+++ b/supplies/116057614-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
     </row>

--- a/supplies/116057614-1.xlsx
+++ b/supplies/116057614-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
     </row>

--- a/supplies/116057614-1.xlsx
+++ b/supplies/116057614-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>

--- a/supplies/116057614-1.xlsx
+++ b/supplies/116057614-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
     </row>

--- a/supplies/116057614-1.xlsx
+++ b/supplies/116057614-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>

--- a/supplies/116057614-1.xlsx
+++ b/supplies/116057614-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>

--- a/supplies/116057614-1.xlsx
+++ b/supplies/116057614-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>

--- a/supplies/116057614-1.xlsx
+++ b/supplies/116057614-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
     </row>

--- a/supplies/116057614-1.xlsx
+++ b/supplies/116057614-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
     </row>

--- a/supplies/116057614-1.xlsx
+++ b/supplies/116057614-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
     </row>

--- a/supplies/116057614-1.xlsx
+++ b/supplies/116057614-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
     </row>

--- a/supplies/116057614-1.xlsx
+++ b/supplies/116057614-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>

--- a/supplies/116057614-1.xlsx
+++ b/supplies/116057614-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>

--- a/supplies/116057614-1.xlsx
+++ b/supplies/116057614-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
     </row>

--- a/supplies/116057614-1.xlsx
+++ b/supplies/116057614-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
     </row>

--- a/supplies/116057614-1.xlsx
+++ b/supplies/116057614-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
     </row>

--- a/supplies/116057614-1.xlsx
+++ b/supplies/116057614-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
     </row>

--- a/supplies/116057614-1.xlsx
+++ b/supplies/116057614-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
     </row>

--- a/supplies/116057614-1.xlsx
+++ b/supplies/116057614-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
